--- a/KW1.xlsx
+++ b/KW1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prac608\Desktop\BO_KW1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476339D6-303B-49C4-92EC-BD3DA20F8758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD06927E-8FF6-4639-A490-8CBCFF53F664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{10D9412E-425A-427C-9571-88D404C725CE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{10D9412E-425A-427C-9571-88D404C725CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Z1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="160">
   <si>
     <t>Wyrób 1</t>
   </si>
@@ -338,13 +338,199 @@
   </si>
   <si>
     <t>x2&gt;=2</t>
+  </si>
+  <si>
+    <t>1*X1+4*X2&lt;=8000</t>
+  </si>
+  <si>
+    <t>6.Metoda geometryczna w rozwiązaniu modelu decyzyjnego</t>
+  </si>
+  <si>
+    <t>x1 i x2&gt;=0 czyli rozwiązanie w 1 ćwartce układu wspólrzędnych</t>
+  </si>
+  <si>
+    <t>Zamiana nierówności warunków ograniczjących na równania</t>
+  </si>
+  <si>
+    <t>RWO1</t>
+  </si>
+  <si>
+    <t>1X1+4X2=8000</t>
+  </si>
+  <si>
+    <t>podstawić 0 za x1 potem za x2</t>
+  </si>
+  <si>
+    <t>RWO2</t>
+  </si>
+  <si>
+    <t>3X1+2X2=9000</t>
+  </si>
+  <si>
+    <t>Część wspólna z warunków brzegowych i ograniczjących jest rozwiązaniem dopuszczalnym</t>
+  </si>
+  <si>
+    <t>Wykres</t>
+  </si>
+  <si>
+    <t>Zbiór rozwiązań dopuszczalnych</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Wykreślenie i przesunięcie izokwanty FC w kierunku optimum(MAX) z zachowaniem styczności ze zbiorem rozwiązań dopuszczalnych</t>
+  </si>
+  <si>
+    <t>izoFC=</t>
+  </si>
+  <si>
+    <t>200*X1+400*X2 =8000</t>
+  </si>
+  <si>
+    <t>dowolna wartość np. z przemnorzenia plus jedno zero</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>Odczytanie z wykresu lub wyznaczenie matematyczne rozwiązania optymalnego</t>
+  </si>
+  <si>
+    <t>X1=</t>
+  </si>
+  <si>
+    <t>X2=</t>
+  </si>
+  <si>
+    <t>Z wykresu odczytane</t>
+  </si>
+  <si>
+    <t>Z układu równań część wspólna RWO1 i RWO2</t>
+  </si>
+  <si>
+    <t>Z wzorów Cramera</t>
+  </si>
+  <si>
+    <t>A=</t>
+  </si>
+  <si>
+    <t>B=</t>
+  </si>
+  <si>
+    <t>A1=</t>
+  </si>
+  <si>
+    <t>A2=</t>
+  </si>
+  <si>
+    <t>Nastęnie policzyć wyznaczniki tych macierzy</t>
+  </si>
+  <si>
+    <t>detA=</t>
+  </si>
+  <si>
+    <t>detA1=</t>
+  </si>
+  <si>
+    <t>detA2=</t>
+  </si>
+  <si>
+    <t>x1=</t>
+  </si>
+  <si>
+    <t>detA1/detA</t>
+  </si>
+  <si>
+    <t>x2=</t>
+  </si>
+  <si>
+    <t>detA2/detA</t>
+  </si>
+  <si>
+    <t>ilość produkcji w1</t>
+  </si>
+  <si>
+    <t>ilość produkcji w2</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>Określenie funkcji celu w rozwiązaniu optymalnym</t>
+  </si>
+  <si>
+    <t>optFC=</t>
+  </si>
+  <si>
+    <t>optymalny maksymalny zysk z wyrobów W1 oraz W2</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>Wykreślenie optFc na wykresie</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>x1 i x2&gt;=0 więc 1 ćwiartka</t>
+  </si>
+  <si>
+    <t>RWO1:</t>
+  </si>
+  <si>
+    <t>RWO2:</t>
+  </si>
+  <si>
+    <t>0,02*x2+0,005&lt;=2</t>
+  </si>
+  <si>
+    <t>RWO3:</t>
+  </si>
+  <si>
+    <t>a31</t>
+  </si>
+  <si>
+    <t>a32</t>
+  </si>
+  <si>
+    <t>izoFC</t>
+  </si>
+  <si>
+    <t>opt:</t>
+  </si>
+  <si>
+    <t>100*60+30*0</t>
+  </si>
+  <si>
+    <t>Cramer pomnięty odczytane z wykresu</t>
+  </si>
+  <si>
+    <t>1 ćwiartka</t>
+  </si>
+  <si>
+    <t>Rwo1:</t>
+  </si>
+  <si>
+    <t>RWoO3:</t>
+  </si>
+  <si>
+    <t>izoFc=</t>
+  </si>
+  <si>
+    <t>W razie co cramer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;zł&quot;"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,8 +539,25 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,6 +567,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,12 +622,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -418,6 +666,3687 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pl-PL"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pl-PL"/>
+              <a:t>Metoda</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pl-PL" baseline="0"/>
+              <a:t> Geometryczna zad.</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>1</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>WO1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z1'!$G$24:$G$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z1'!$H$24:$H$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-06D4-4174-A83D-B4F56B94642F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>WO2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z1'!$G$28:$G$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z1'!$H$28:$H$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-06D4-4174-A83D-B4F56B94642F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>izoFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z1'!$H$50:$H$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z1'!$I$50:$I$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-06D4-4174-A83D-B4F56B94642F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>optFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z1'!$F$79:$F$80</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z1'!$G$79:$G$80</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-06D4-4174-A83D-B4F56B94642F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="399751536"/>
+        <c:axId val="399753616"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="399751536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>X1 </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="399753616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="399753616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>X2</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="399751536"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="500"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.79323730367037448"/>
+          <c:y val="0.40409595996762093"/>
+          <c:w val="0.13779506460406277"/>
+          <c:h val="0.37067804745164684"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pl-PL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pl-PL"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pl-PL"/>
+              <a:t>Zad2.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.38535411198600172"/>
+          <c:y val="3.2407407407407406E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>RWO1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z2'!$E$17:$E$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z2'!$F$17:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C505-4CB3-A8DE-C1BBCCB51F34}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>RWO2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z2'!$E$22:$E$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z2'!$F$22:$F$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C505-4CB3-A8DE-C1BBCCB51F34}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>RWO3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z2'!$E$27:$E$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z2'!$F$27:$F$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C505-4CB3-A8DE-C1BBCCB51F34}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>izoFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z2'!$F$45:$F$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z2'!$G$45:$G$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-C505-4CB3-A8DE-C1BBCCB51F34}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>optFc</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z2'!$F$53:$F$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z2'!$G$53:$G$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-C505-4CB3-A8DE-C1BBCCB51F34}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="990930432"/>
+        <c:axId val="990934176"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="990930432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>X</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.450047009049242"/>
+              <c:y val="0.87322187048824995"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="990934176"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="990934176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>Y</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="990930432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pl-PL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pl-PL"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>RWO1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z3'!$F$16:$F$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z3'!$G$16:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-383A-4730-BF6C-DF34CE4AC0E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>RWO2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z3'!$F$22:$F$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>84</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z3'!$G$22:$G$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-383A-4730-BF6C-DF34CE4AC0E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>RWO3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z3'!$F$26:$F$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>225</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z3'!$G$26:$G$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-383A-4730-BF6C-DF34CE4AC0E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>izoFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Z3'!$E$46:$E$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Z3'!$F$46:$F$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-383A-4730-BF6C-DF34CE4AC0E8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="990930432"/>
+        <c:axId val="990941248"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="990930432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="990941248"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="20"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="990941248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="990930432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="10"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pl-PL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -428,8 +4357,8 @@
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>105205</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>425245</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>15241</xdr:rowOff>
     </xdr:to>
@@ -477,8 +4406,8 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>152640</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="Pismo odręczne 17">
@@ -497,7 +4426,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="Pismo odręczne 17">
@@ -519,6 +4448,1075 @@
             <a:xfrm>
               <a:off x="4585680" y="5264280"/>
               <a:ext cx="18000" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Wykres 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEAC86BA-C92E-4206-9456-812B03C1D76C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228480</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>7560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228840</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>7920</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="8" name="Pismo odręczne 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7353C42F-F764-479C-93B6-F532CAADF726}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2666880" y="7139880"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="Pismo odręczne 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7353C42F-F764-479C-93B6-F532CAADF726}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2613240" y="7032240"/>
+              <a:ext cx="108000" cy="216000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>21120</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>169680</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>31320</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="9" name="Pismo odręczne 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B01BDF6-7244-4B36-AD1F-DE2D9CE393B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2459520" y="6789240"/>
+            <a:ext cx="758160" cy="374400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="9" name="Pismo odręczne 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B01BDF6-7244-4B36-AD1F-DE2D9CE393B8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2405880" y="6681600"/>
+              <a:ext cx="865800" cy="590040"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>45600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>45360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>66480</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="12" name="Pismo odręczne 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD572A5-3AD9-402B-B1F1-E5C834A37550}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2484000" y="6994800"/>
+            <a:ext cx="20880" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="12" name="Pismo odręczne 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD572A5-3AD9-402B-B1F1-E5C834A37550}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2475000" y="6986160"/>
+              <a:ext cx="38520" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>182760</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>45360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>183120</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="13" name="Pismo odręczne 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0676752B-E69A-4E70-8FC7-10F722133D1B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2621160" y="6994800"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="13" name="Pismo odręczne 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0676752B-E69A-4E70-8FC7-10F722133D1B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2612160" y="6986160"/>
+              <a:ext cx="18000" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>53280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>259440</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>53640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="14" name="Pismo odręczne 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E11925D2-195B-4E40-9E79-0D69D391FF2D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2697480" y="7002720"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="14" name="Pismo odręczne 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E11925D2-195B-4E40-9E79-0D69D391FF2D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2688480" y="6994080"/>
+              <a:ext cx="18000" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>335040</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>53280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>338280</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>53640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="15" name="Pismo odręczne 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0EBCBE1-F61D-4709-ABB0-BF1BA4275196}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2773440" y="7002720"/>
+            <a:ext cx="3240" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="15" name="Pismo odręczne 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0EBCBE1-F61D-4709-ABB0-BF1BA4275196}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2764440" y="6994080"/>
+              <a:ext cx="20880" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>411360</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>53280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>425400</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>53640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="16" name="Pismo odręczne 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE38A395-5D12-4C2B-908C-441580A12301}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2849760" y="7002720"/>
+            <a:ext cx="14040" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="16" name="Pismo odręczne 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE38A395-5D12-4C2B-908C-441580A12301}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2840760" y="6994080"/>
+              <a:ext cx="31680" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>556080</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>60840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>556440</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>61200</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="17" name="Pismo odręczne 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF8BE59-A9DB-4456-9CB0-DCD7BA06142E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2994480" y="7010280"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="17" name="Pismo odręczne 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF8BE59-A9DB-4456-9CB0-DCD7BA06142E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2985480" y="7001640"/>
+              <a:ext cx="18000" cy="18000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7320</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>60840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7680</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="23" name="Pismo odręczne 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{912EA01F-5051-423F-AC6F-280C6BFC4987}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3055320" y="7193160"/>
+            <a:ext cx="360" cy="3240"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="23" name="Pismo odręczne 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{912EA01F-5051-423F-AC6F-280C6BFC4987}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3046320" y="7184520"/>
+              <a:ext cx="18000" cy="20880"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7320</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>16560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7680</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>38160</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="24" name="Pismo odręczne 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E664F82E-B122-4724-B1EE-2B252F70BEB2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3055320" y="7148880"/>
+            <a:ext cx="360" cy="21600"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="24" name="Pismo odręczne 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E664F82E-B122-4724-B1EE-2B252F70BEB2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3046320" y="7139880"/>
+              <a:ext cx="18000" cy="39240"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>586680</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>109080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7680</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>140400</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="27" name="Pismo odręczne 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B8ECBAF-5DF4-407D-9914-39FDCE68356D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3025080" y="7058520"/>
+            <a:ext cx="30600" cy="31320"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="27" name="Pismo odręczne 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B8ECBAF-5DF4-407D-9914-39FDCE68356D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3016080" y="7049520"/>
+              <a:ext cx="48240" cy="48960"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>601800</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>45360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7680</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>76320</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="28" name="Pismo odręczne 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A3F70D5-F9A4-4C69-8CED-4719F02A486E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3040200" y="6994800"/>
+            <a:ext cx="15480" cy="30960"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="28" name="Pismo odręczne 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A3F70D5-F9A4-4C69-8CED-4719F02A486E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3031200" y="6986160"/>
+              <a:ext cx="33120" cy="48600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>373380</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Łącznik prosty 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10ED5996-A838-4A41-BB9F-73BCD71D2258}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2202180" y="6515100"/>
+          <a:ext cx="2423160" cy="975360"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571200</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>91080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>602160</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>99360</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="43" name="Pismo odręczne 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644928C8-FDA3-4184-87BD-708D63E4EABB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3009600" y="6857640"/>
+            <a:ext cx="30960" cy="8280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="43" name="Pismo odręczne 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644928C8-FDA3-4184-87BD-708D63E4EABB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2991600" y="6840000"/>
+              <a:ext cx="66600" cy="43920"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>583440</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>82800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>604680</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>107640</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="44" name="Pismo odręczne 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{314429B7-0A7B-4F6F-805A-DDEC32BF6DBE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="3021840" y="6849360"/>
+            <a:ext cx="21240" cy="24840"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="44" name="Pismo odręczne 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{314429B7-0A7B-4F6F-805A-DDEC32BF6DBE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3003840" y="6831720"/>
+              <a:ext cx="56880" cy="60480"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>670680</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>891360</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>32040</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="45" name="Pismo odręczne 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B38D2B1-AE7F-47FC-AB1E-6C2FD399F913}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="2499480" y="6805080"/>
+            <a:ext cx="220680" cy="359280"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="45" name="Pismo odręczne 44">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B38D2B1-AE7F-47FC-AB1E-6C2FD399F913}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2445480" y="6697440"/>
+              <a:ext cx="328320" cy="574920"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -578,6 +5576,92 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Wykres 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20B0F4CA-B02A-4ABA-828E-ED3686DB820C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Łącznik prosty 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B669FE65-BCB1-40A3-B2C5-79F65CC13E20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="777240" y="6758940"/>
+          <a:ext cx="1927860" cy="853440"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -591,8 +5675,8 @@
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>87261</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>376821</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>129541</xdr:rowOff>
     </xdr:to>
@@ -625,6 +5709,92 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Wykres 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DC42269-DAA8-446B-99B7-3C60C59C885F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Łącznik prosty 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{791FE994-928B-48A3-9737-0D154F713D29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="807720" y="6073140"/>
+          <a:ext cx="2385060" cy="1737360"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -743,6 +5913,436 @@
         </inkml:channelProperties>
       </inkml:inkSource>
       <inkml:timestamp xml:id="ts0" timeString="2026-03-09T07:24:25.956"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink10.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:05.279"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'0'3,"0"2</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink11.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:05.866"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 60,'0'-4,"0"-8,0-9,0-2</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:03.622"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 78,'3'0,"2"0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1231.47">22 78,'-1'3,"1"2</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2637.67">85 78,'0'0,"0"-4,0-4,0-5,0-4,0-2,0 2</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink13.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:03.101"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">43 44</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1326.54">1 86</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3494.21">43 1</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink14.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:29:48.461"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">65 23,'-1'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1568.13">86 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1915.69">86 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2248.87">86 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2249.87">86 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2582.03">86 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2913.44">86 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3247.03">65 1,'-1'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3248.03">65 1,'-4'0,"-1"0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3598.65">44 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3599.65">44 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3932.47">44 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3933.47">44 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4264.17">44 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4265.17">44 1,'-4'0,"-5"0,0 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4612.19">1 1,'0'0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink15.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:30:00.685"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">31 3,'-5'-1,"14"0,-3 1,-18 2,12-2,-1 0,1 0,-1 0,1 0,0 0,-1 0,1 0,-1 1,1-1,-1 0,1 0,0 0,-1 0,1 1,0-1,-1 0,1 0,-1 0,1 1,0-1,0 0,-1 1,1-1,0 0,-1 1,1-1,0 1,0-1,0 0,0 1,-1-1,1 1,0-1,0 0,0 1,0 0,7 15,2 3,-9-19,0 1,0-1,0 1,0 0,0-1,0 1,0-1,0 1,-1-1,1 1,0 0,0-1,-1 1,1-1,0 1,0-1,-1 1,1-1,-1 0,1 1,0-1,-1 1,1-1,-1 0,1 1,-1-1,1 0,-1 0,1 1,-1-1,0 0,0 0,-15 4,9-2,18-2,-8 1,-1-1,0-1,1 1,-1 0,0 0,1-1,-1 1,0-1,0 0,0 0,1 0,-1 0,0 0,3-2,-4 1,0 1,0-1,0 0,0 1,0-1,0 0,-1 0,1 0,-1 1,1-1,-1 0,0 0,0 0,1 0,-2 0,1 0,0 0,-1-2,0-10</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink16.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:43:01.890"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">85 84,'1'0,"1"0,0 1,0-1,0 1,0 0,0 0,-1 0,1 0,0 0,-1 0,1 0,0 0,-1 0,0 1,1-1,-1 1,0-1,0 1,0 0,1-1,-2 1,1 0,0 0,0-1,-1 1,1 0,-1 0,1 0,-1 0,0 3,3 10,-2 0,0 28,-1-35,-3 122,5 123,1-235,0-1,2 0,0 0,0 0,2 0,13 25,7 17,-24-50,-1 0,0 0,0 0,-1 1,-1-1,1 0,-3 19,1-19,1 1,0 0,0 0,1-1,0 1,4 11,-5-20,1 1,0 0,-1 0,1-1,0 1,0 0,0-1,0 1,1-1,-1 0,0 1,1-1,-1 0,1 0,-1 0,1 0,-1 0,1 0,0 0,0 0,-1-1,1 1,0-1,0 1,0-1,0 0,-1 1,1-1,0 0,0 0,0-1,0 1,0 0,-1-1,1 1,4-2,-3 1,1 0,0-1,-1 0,1 1,-1-1,1 0,-1 0,0-1,0 1,0-1,0 0,0 1,-1-1,1-1,-1 1,0 0,2-4,0-4,-2 0,1 0,-2-1,1 1,-1-16,3-22,2-16,-2-1,-5-80,3-77,8 166,-6 41,-1 0,1-22,-3 8,0-46,-1 69,-1 1,1 0,-2-1,1 1,-1 0,0 0,0 0,-1 0,-3-7,6 12,0 1,-1-1,1 0,0 0,-1 1,1-1,-1 0,1 1,-1-1,1 1,-1-1,1 0,-1 1,0-1,1 1,-1 0,0-1,1 1,-1-1,0 1,1 0,-1 0,0-1,0 1,0 0,1 0,-1 0,0 0,0 0,1 0,-2 0,1 1,-1 0,1 0,0 0,0 0,0 0,0 0,0 1,1-1,-1 0,0 0,0 1,1-1,-1 0,0 4,-2 6,0 1,-3 23,3 240,6-141,-4-93,-1-1,-12 59,12-87,1 1,0-1,1 0,0 0,1 1,1-1,0 0,0 0,1 0,1 0,0-1,0 1,11 18,-11-23,0 0,0-1,1 1,0-1,0 0,1 0,0 0,0-1,0 0,0 0,1-1,0 0,0 0,0 0,0-1,1 0,-1 0,1-1,0 0,0 0,14 0,103-5,-470 2,300-3,0-2,1-2,-63-20,85 20,18 6,16 4,-7-1,13 2,0 0,0-1,32 0,-45-2,-1 0,0 0,0-1,0 0,0 0,0 0,0 0,0-1,0 1,0-1,-1 0,1 0,0 0,-1-1,0 1,0-1,1 0,-2 0,1 0,0 0,-1 0,4-7,45-80,-28 51,-2-1,32-81,-32 68,2 0,3 2,50-75,-30 50,-37 63,-6 9,-1 1,1-1,-1 0,0 0,0 1,0-1,-1-1,1 1,0-7,-2 11,0-1,0 1,0-1,0 1,0 0,0-1,0 1,0-1,0 1,0 0,0-1,0 1,-1 0,1-1,0 1,0 0,0-1,-1 1,1 0,0-1,0 1,-1 0,1 0,0-1,-1 1,1 0,0 0,-1 0,1-1,0 1,-1 0,1 0,-1 0,1 0,-1 0,-19 2,-18 14,37-15,-380 182,379-181,1-1,-1 0,0 0,0 0,0 0,1-1,-1 1,0 0,0-1,0 0,0 1,0-1,0 0,0 0,0 0,0 0,0 0,0-1,0 1,0 0,0-1,0 0,0 1,-2-2,2 0,1 0,-1 0,0-1,1 1,-1 0,1-1,0 1,0-1,0 1,0-1,1 0,-1 1,0-1,1 0,0 1,0-1,0-3,1 1,3 16,8 35,1 2,-8-24,0 0,-2 0,-1 1,0-1,-4 32,2-41,0 3</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:21:34.979"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'0'0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:21:43.219"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">48 1,'-2'0,"1"0,0 1,0-1,0 1,0-1,0 1,0 0,0-1,1 1,-1 0,0 0,0 0,0 0,1-1,-1 1,0 0,1 0,-1 0,1 0,-1 1,1-1,0 0,-1 0,1 2,-9 38,6-27,-4 32,1 0,3 1,5 89,0-42,-1-76,1-1,1 1,0-1,2 1,0-1,12 27,-2-3,-7-15,8 54,1 2,-13-63,-1-6,1-1,8 21,-10-29,1 0,-1 0,0 0,1-1,0 1,0-1,0 0,0 1,1-1,-1-1,7 5,1-1,0-2,0 1,0-1,0-1,1 0,0-1,21 2,-14-2,0 1,18 6,11 4,1-1,84 7,135-15,-145-6,-95 0,46-7,-45 4,42-1,838 7,-908-1,1 0,0 0,0 0,-1 0,1 0,0-1,-1 1,1-1,0 1,-1-1,1 1,2-2,-4 2,0-1,0 1,1 0,-1-1,0 1,0 0,0 0,0-1,1 1,-1 0,0-1,0 1,0-1,0 1,0 0,0-1,0 1,0 0,0-1,0 1,0 0,0-1,0 1,0-1,-1 1,1 0,0-1,0 1,0 0,0 0,-1-1,1 1,0-1,-5-4,0 0,1 1,-1-1,-10-6,-135-105,95 82,41 27,1-1,-21-15,-15-21,21 19,-49-34,63 49,1-1,0 0,-17-20,22 21,-1 1,-1 0,0 0,0 1,-1 0,0 1,-13-7,-147-63,-14 13,180 62,-48-14,-1 2,-93-11,125 23,1-1,1-1,-1-1,0-1,1-1,-29-13,16 8,0 1,0 2,-49-7,61 12,-280-59,293 61,-1 0,1 0,-1 1,0 0,1 1,-11 1,18-1,-1 0,1 0,-1 0,1 1,0-1,-1 1,1-1,0 1,-1 0,1-1,0 1,0 0,0 0,-1 0,1 0,0 0,-1 2,1-2,0 1,1 0,-1-1,1 1,0 0,-1 0,1-1,0 1,0 0,0-1,0 1,0 0,1 0,-1-1,0 1,1 0,-1-1,2 4,4 8,1 0,0 0,1-1,0 0,1 0,0-1,1 0,0-1,15 13,9 4,68 42,-83-60,1 0,-1-1,1-1,1-1,30 5,-21-4,49 16,-42-10,60 12,26 10,-99-29,-1-1,1-1,0-1,0-1,0-1,46-3,-13 0,-35 2</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:27:59.648"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'3'0,"5"0,5 0,4 0,-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:00.158"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'0'0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:00.670"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'0'0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink7.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:01.158"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'3'0,"2"0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink8.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:01.550"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'3'0,"5"0,5 0,0 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink9.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-16T07:28:02.180"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.05" units="cm"/>
@@ -1052,8 +6652,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F75035C-00A0-4345-910D-8DEFF3C6FD49}">
-  <dimension ref="B2:T28"/>
+  <dimension ref="B2:T80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:20" x14ac:dyDescent="0.3">
       <c r="L2" t="s">
@@ -1235,19 +6838,39 @@
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="L19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
       <c r="L20" t="s">
         <v>31</v>
       </c>
       <c r="M20" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
       <c r="L21" t="s">
         <v>32</v>
       </c>
@@ -1256,11 +6879,28 @@
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
       <c r="L22" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="G23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="L23" t="s">
         <v>36</v>
       </c>
@@ -1269,11 +6909,43 @@
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <f>F25/E25</f>
+        <v>2000</v>
+      </c>
       <c r="L24" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>8000</v>
+      </c>
+      <c r="G25" s="5">
+        <f>F25/D25</f>
+        <v>8000</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0</v>
+      </c>
       <c r="L25" t="s">
         <v>17</v>
       </c>
@@ -1290,6 +6962,18 @@
       </c>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="L27" t="s">
         <v>32</v>
       </c>
@@ -1298,11 +6982,385 @@
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5">
+        <f>F29/E29</f>
+        <v>4500</v>
+      </c>
       <c r="L28" t="s">
         <v>36</v>
       </c>
       <c r="M28" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>9000</v>
+      </c>
+      <c r="G29" s="5">
+        <f>F29/D29</f>
+        <v>3000</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" t="s">
+        <v>114</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E50">
+        <v>200</v>
+      </c>
+      <c r="F50">
+        <v>400</v>
+      </c>
+      <c r="G50" s="8">
+        <v>800000</v>
+      </c>
+      <c r="H50" s="5">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5">
+        <f>G50/F50</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H51" s="5">
+        <f>G50/E50</f>
+        <v>4000</v>
+      </c>
+      <c r="I51" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B52" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C54" t="s">
+        <v>119</v>
+      </c>
+      <c r="D54">
+        <v>1500</v>
+      </c>
+      <c r="F54" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C56" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C57" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C58" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C59" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C60" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="11">
+        <v>1</v>
+      </c>
+      <c r="E60" s="11">
+        <v>4</v>
+      </c>
+      <c r="G60" t="s">
+        <v>124</v>
+      </c>
+      <c r="H60" s="12">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D61" s="11">
+        <v>3</v>
+      </c>
+      <c r="E61" s="11">
+        <v>2</v>
+      </c>
+      <c r="H61" s="12">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C63" t="s">
+        <v>125</v>
+      </c>
+      <c r="D63" s="12">
+        <v>8000</v>
+      </c>
+      <c r="E63" s="11">
+        <v>4</v>
+      </c>
+      <c r="G63" t="s">
+        <v>126</v>
+      </c>
+      <c r="H63" s="11">
+        <v>1</v>
+      </c>
+      <c r="I63" s="12">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D64" s="12">
+        <v>9000</v>
+      </c>
+      <c r="E64" s="11">
+        <v>2</v>
+      </c>
+      <c r="H64" s="11">
+        <v>3</v>
+      </c>
+      <c r="I64" s="12">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C66" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C67" t="s">
+        <v>128</v>
+      </c>
+      <c r="D67">
+        <f>MDETERM(D60:E61)</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C68" t="s">
+        <v>129</v>
+      </c>
+      <c r="D68">
+        <f>MDETERM(D63:E64)</f>
+        <v>-20000</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C69" t="s">
+        <v>130</v>
+      </c>
+      <c r="D69">
+        <f>MDETERM(H63:I64)</f>
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C71" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E71" s="14"/>
+      <c r="F71" s="13">
+        <f>D68/D67</f>
+        <v>2000</v>
+      </c>
+      <c r="G71" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C72" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E72" s="14"/>
+      <c r="F72" s="13">
+        <f>D69/D67</f>
+        <v>1500</v>
+      </c>
+      <c r="G72" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B74" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C74" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C76" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="D76" s="15">
+        <f>200*F71+400*F72</f>
+        <v>1000000</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B77" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C79">
+        <v>200</v>
+      </c>
+      <c r="D79">
+        <v>400</v>
+      </c>
+      <c r="E79">
+        <v>1000000</v>
+      </c>
+      <c r="F79" s="5">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5">
+        <f>E79/D79</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F80" s="5">
+        <f>E79/C79</f>
+        <v>5000</v>
+      </c>
+      <c r="G80" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1313,15 +7371,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6773E626-73A8-4CCA-8956-B7CE8B17336F}">
-  <dimension ref="J2:K25"/>
+  <dimension ref="A2:K54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J3" t="s">
         <v>40</v>
       </c>
@@ -1329,7 +7387,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J4" t="s">
         <v>41</v>
       </c>
@@ -1337,12 +7395,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J6" t="s">
         <v>11</v>
       </c>
@@ -1350,7 +7408,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J7" t="s">
         <v>12</v>
       </c>
@@ -1358,12 +7416,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J9" t="s">
         <v>17</v>
       </c>
@@ -1371,12 +7429,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J11" t="s">
         <v>20</v>
       </c>
@@ -1384,7 +7442,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J12" t="s">
         <v>21</v>
       </c>
@@ -1392,7 +7450,13 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" t="s">
+        <v>144</v>
+      </c>
       <c r="J13" t="s">
         <v>48</v>
       </c>
@@ -1400,7 +7464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J14" t="s">
         <v>22</v>
       </c>
@@ -1408,7 +7472,16 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="15" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
       <c r="J15" t="s">
         <v>23</v>
       </c>
@@ -1416,7 +7489,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="16" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
       <c r="J16" t="s">
         <v>49</v>
       </c>
@@ -1424,12 +7503,44 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f>D18/C18</f>
+        <v>1000</v>
+      </c>
       <c r="J17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>0.01</v>
+      </c>
+      <c r="C18">
+        <v>2E-3</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <f>D18/B18</f>
+        <v>200</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
       <c r="J18" t="s">
         <v>28</v>
       </c>
@@ -1437,7 +7548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J19" t="s">
         <v>29</v>
       </c>
@@ -1445,7 +7556,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" t="s">
+        <v>147</v>
+      </c>
       <c r="J20" t="s">
         <v>51</v>
       </c>
@@ -1453,12 +7570,34 @@
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>41</v>
+      </c>
       <c r="J21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f>D23/C23</f>
+        <v>400</v>
+      </c>
       <c r="J22" t="s">
         <v>31</v>
       </c>
@@ -1466,7 +7605,23 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>0.02</v>
+      </c>
+      <c r="C23">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <f>D23/B23</f>
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
       <c r="J23" t="s">
         <v>54</v>
       </c>
@@ -1474,7 +7629,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="J24" t="s">
         <v>56</v>
       </c>
@@ -1482,12 +7637,190 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
+      </c>
       <c r="J25" t="s">
         <v>70</v>
       </c>
       <c r="K25" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f>D28/C28</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>180</v>
+      </c>
+      <c r="E28">
+        <f>D28/B28</f>
+        <v>60</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>151</v>
+      </c>
+      <c r="C44" t="s">
+        <v>46</v>
+      </c>
+      <c r="F44" t="s">
+        <v>58</v>
+      </c>
+      <c r="G44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <f>E46/D46</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C46">
+        <v>100</v>
+      </c>
+      <c r="D46">
+        <v>30</v>
+      </c>
+      <c r="E46">
+        <f>C46*D46</f>
+        <v>3000</v>
+      </c>
+      <c r="F46">
+        <f>E46/C46</f>
+        <v>30</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49">
+        <v>60</v>
+      </c>
+      <c r="H49" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C51" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13">
+        <f>6000</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F52" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C53">
+        <v>6000</v>
+      </c>
+      <c r="D53">
+        <v>100</v>
+      </c>
+      <c r="E53">
+        <v>30</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <f>C53/E53</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F54">
+        <f>C53/D53</f>
+        <v>60</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1498,10 +7831,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1389125F-4D16-4B83-9402-0C5CDA76E2BD}">
-  <dimension ref="K2:L19"/>
+  <dimension ref="A2:L63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K2" t="s">
         <v>58</v>
       </c>
@@ -1509,7 +7845,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K3" t="s">
         <v>59</v>
       </c>
@@ -1517,7 +7853,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K4" t="s">
         <v>62</v>
       </c>
@@ -1525,7 +7861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K5" t="s">
         <v>63</v>
       </c>
@@ -1533,7 +7869,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K6" t="s">
         <v>17</v>
       </c>
@@ -1541,7 +7877,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K7" t="s">
         <v>20</v>
       </c>
@@ -1549,7 +7885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K8" t="s">
         <v>21</v>
       </c>
@@ -1557,7 +7893,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K9" t="s">
         <v>48</v>
       </c>
@@ -1565,7 +7901,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K10" t="s">
         <v>22</v>
       </c>
@@ -1573,7 +7909,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K11" t="s">
         <v>23</v>
       </c>
@@ -1581,7 +7917,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K12" t="s">
         <v>49</v>
       </c>
@@ -1589,7 +7925,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="13" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K13" t="s">
         <v>28</v>
       </c>
@@ -1597,7 +7933,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>155</v>
+      </c>
       <c r="K14" t="s">
         <v>29</v>
       </c>
@@ -1605,7 +7947,19 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" t="s">
+        <v>41</v>
+      </c>
       <c r="K15" t="s">
         <v>51</v>
       </c>
@@ -1613,7 +7967,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <f>E18/D18</f>
+        <v>80</v>
+      </c>
       <c r="K16" t="s">
         <v>31</v>
       </c>
@@ -1621,7 +7982,23 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17">
+        <f>E18/C18</f>
+        <v>40</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
       <c r="K17" t="s">
         <v>32</v>
       </c>
@@ -1629,7 +8006,16 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>0.5</v>
+      </c>
+      <c r="E18">
+        <v>40</v>
+      </c>
       <c r="K18" t="s">
         <v>56</v>
       </c>
@@ -1637,12 +8023,316 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K19" t="s">
         <v>68</v>
       </c>
       <c r="L19" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <f>E23/D23</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C23">
+        <v>0.5</v>
+      </c>
+      <c r="D23">
+        <v>0.6</v>
+      </c>
+      <c r="E23">
+        <v>42</v>
+      </c>
+      <c r="F23">
+        <f>E23/C23</f>
+        <v>84</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" t="s">
+        <v>150</v>
+      </c>
+      <c r="E26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f>E27/D27</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C27">
+        <v>0.2</v>
+      </c>
+      <c r="D27">
+        <v>0.3</v>
+      </c>
+      <c r="E27">
+        <v>45</v>
+      </c>
+      <c r="F27">
+        <f>E27/C27</f>
+        <v>225</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <f>D47/C47</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B47">
+        <v>20</v>
+      </c>
+      <c r="C47">
+        <v>30</v>
+      </c>
+      <c r="D47">
+        <f>C47*B47</f>
+        <v>600</v>
+      </c>
+      <c r="E47">
+        <f>D47/B47</f>
+        <v>30</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>159</v>
+      </c>
+      <c r="G53" t="s">
+        <v>31</v>
+      </c>
+      <c r="H53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G54" t="s">
+        <v>32</v>
+      </c>
+      <c r="H54" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>0.5</v>
+      </c>
+      <c r="G55" t="s">
+        <v>56</v>
+      </c>
+      <c r="H55" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C56">
+        <v>0.5</v>
+      </c>
+      <c r="D56">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C57">
+        <v>0.2</v>
+      </c>
+      <c r="D57">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59">
+        <v>40</v>
+      </c>
+      <c r="E59" t="s">
+        <v>125</v>
+      </c>
+      <c r="F59">
+        <v>40</v>
+      </c>
+      <c r="G59">
+        <v>0.5</v>
+      </c>
+      <c r="I59" t="s">
+        <v>126</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C60">
+        <v>42</v>
+      </c>
+      <c r="F60">
+        <v>42</v>
+      </c>
+      <c r="G60">
+        <v>0.6</v>
+      </c>
+      <c r="J60">
+        <v>0.5</v>
+      </c>
+      <c r="K60">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C61">
+        <v>45</v>
+      </c>
+      <c r="F61">
+        <v>45</v>
+      </c>
+      <c r="G61">
+        <v>0.3</v>
+      </c>
+      <c r="J61">
+        <v>0.2</v>
+      </c>
+      <c r="K61">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" t="e">
+        <f>MDETERM(C55:D57)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/KW1.xlsx
+++ b/KW1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prac608\Desktop\BO_KW1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD06927E-8FF6-4639-A490-8CBCFF53F664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912B9624-80DF-46C8-AD1D-38DF1D3C548B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{10D9412E-425A-427C-9571-88D404C725CE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{10D9412E-425A-427C-9571-88D404C725CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Z1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Z3" sheetId="3" r:id="rId3"/>
     <sheet name="Z1min" sheetId="4" r:id="rId4"/>
     <sheet name="Z2min" sheetId="5" r:id="rId5"/>
+    <sheet name="Z3min" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="201">
   <si>
     <t>Wyrób 1</t>
   </si>
@@ -521,6 +522,129 @@
   </si>
   <si>
     <t>W razie co cramer</t>
+  </si>
+  <si>
+    <t>10x1+x2=100</t>
+  </si>
+  <si>
+    <t>X1+10x2=100</t>
+  </si>
+  <si>
+    <t>RWO3</t>
+  </si>
+  <si>
+    <t>10x1+10x2=300</t>
+  </si>
+  <si>
+    <t>izo fc</t>
+  </si>
+  <si>
+    <t>5x1+8x2-&gt;min</t>
+  </si>
+  <si>
+    <t>Cramer</t>
+  </si>
+  <si>
+    <t>X1+10x2=200</t>
+  </si>
+  <si>
+    <t>DetA1=</t>
+  </si>
+  <si>
+    <t>DetA2=</t>
+  </si>
+  <si>
+    <t>DetA=</t>
+  </si>
+  <si>
+    <t>optFC</t>
+  </si>
+  <si>
+    <t>OPTFC</t>
+  </si>
+  <si>
+    <t>5x1+8x2=193,94</t>
+  </si>
+  <si>
+    <t>30x1+60x2=480</t>
+  </si>
+  <si>
+    <t>40x1+15x2=240</t>
+  </si>
+  <si>
+    <t>5x1+10x2</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>Wb1</t>
+  </si>
+  <si>
+    <t>dpwolna wartosc</t>
+  </si>
+  <si>
+    <t>wb2</t>
+  </si>
+  <si>
+    <t>tu coś nie gra</t>
+  </si>
+  <si>
+    <t>Z1</t>
+  </si>
+  <si>
+    <t>Zap</t>
+  </si>
+  <si>
+    <t>Z2</t>
+  </si>
+  <si>
+    <t>Wapn</t>
+  </si>
+  <si>
+    <t>Proteiny</t>
+  </si>
+  <si>
+    <t>Wit A</t>
+  </si>
+  <si>
+    <t>Cena</t>
+  </si>
+  <si>
+    <t>c1*x1+c2*x2``min</t>
+  </si>
+  <si>
+    <t>WB:x1,x2&gt;=0</t>
+  </si>
+  <si>
+    <t>WO1</t>
+  </si>
+  <si>
+    <t>WO2</t>
+  </si>
+  <si>
+    <t>WO3</t>
+  </si>
+  <si>
+    <t>10x1+4x2&gt;=20</t>
+  </si>
+  <si>
+    <t>5x1+5x2&gt;=20</t>
+  </si>
+  <si>
+    <t>2x1+6x2&gt;=12</t>
+  </si>
+  <si>
+    <t>IzoFC</t>
+  </si>
+  <si>
+    <t>Fc=</t>
+  </si>
+  <si>
+    <t>OptFc=</t>
+  </si>
+  <si>
+    <t>0,6*x1+1*x2=2,80</t>
   </si>
 </sst>
 </file>
@@ -528,7 +652,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;zł&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;zł&quot;"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -622,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -648,7 +772,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -2679,6 +2805,2270 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pl-PL"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pl-PL"/>
+              <a:t>Metoda</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pl-PL" baseline="0"/>
+              <a:t> gemoetryczna zad1. min</a:t>
+            </a:r>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>RWO1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z1min!$E$19:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z1min!$F$19:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1DE2-497C-BD1A-CE7839E18BDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>RWO2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z1min!$F$23:$F$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z1min!$G$23:$G$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1DE2-497C-BD1A-CE7839E18BDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>RWO3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z1min!$F$27:$F$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z1min!$G$27:$G$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1DE2-497C-BD1A-CE7839E18BDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>IZOFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z1min!$F$32:$F$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z1min!$G$32:$G$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1DE2-497C-BD1A-CE7839E18BDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>OPTFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z1min!$I$48:$I$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38.787999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z1min!$J$48:$J$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>24.2425</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1DE2-497C-BD1A-CE7839E18BDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="861360848"/>
+        <c:axId val="735028336"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="861360848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="200"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>X1-ilość karmy</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="735028336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="10"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="735028336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>X2-ilość</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pl-PL" baseline="0"/>
+                  <a:t> karmy2</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="861360848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pl-PL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pl-PL"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pl-PL"/>
+              <a:t>Zadanie</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pl-PL" baseline="0"/>
+              <a:t> 2min</a:t>
+            </a:r>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>RWO1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z2min!$E$21:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z2min!$F$21:$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-094B-4BE8-9A13-600D20E05576}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>RWO2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z2min!$E$25:$E$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z2min!$F$25:$F$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-094B-4BE8-9A13-600D20E05576}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>IZOFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z2min!$E$29:$E$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z2min!$F$29:$F$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-094B-4BE8-9A13-600D20E05576}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>WB1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z2min!$J$31:$J$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z2min!$K$31:$K$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-094B-4BE8-9A13-600D20E05576}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>WB2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z2min!$J$34:$J$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z2min!$K$34:$K$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-094B-4BE8-9A13-600D20E05576}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>OPTFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z2min!$P$37:$P$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z2min!$Q$37:$Q$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-094B-4BE8-9A13-600D20E05576}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="742383072"/>
+        <c:axId val="742385152"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="742383072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="50"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>P1</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.46582524059492564"/>
+              <c:y val="0.77277704870224551"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="742385152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="742385152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="50"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>P2</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="742383072"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pl-PL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pl-PL"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.02309061330917E-2"/>
+          <c:y val="7.8703703703703706E-2"/>
+          <c:w val="0.90286351706036749"/>
+          <c:h val="0.73577136191309422"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>RWO1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z3min!$E$27:$E$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z3min!$F$27:$F$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-58E4-45E6-9F6B-DBBAD7DE92F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>RWO2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z3min!$E$31:$E$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z3min!$F$31:$F$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-58E4-45E6-9F6B-DBBAD7DE92F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>RWO3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z3min!$E$35:$E$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z3min!$F$35:$F$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-58E4-45E6-9F6B-DBBAD7DE92F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>IzoFc</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z3min!$E$41:$E$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z3min!$F$41:$F$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-58E4-45E6-9F6B-DBBAD7DE92F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>OptFC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Z3min!$K$55:$K$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.666666666666667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Z3min!$L$55:$L$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-58E4-45E6-9F6B-DBBAD7DE92F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1371911360"/>
+        <c:axId val="1371934240"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1371911360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="3.8771002041034446E-2"/>
+              <c:y val="0.88509314682579698"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1371934240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1371934240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pl-PL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1371911360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.20517503185404995"/>
+          <c:y val="0.89183112879225368"/>
+          <c:w val="0.59826876844014409"/>
+          <c:h val="6.5483578231417233E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pl-PL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2799,6 +5189,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3832,6 +6342,1554 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4507,8 +8565,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>7920</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Pismo odręczne 7">
@@ -4527,7 +8585,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Pismo odręczne 7">
@@ -4572,8 +8630,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>31320</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="9" name="Pismo odręczne 8">
@@ -4592,7 +8650,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="9" name="Pismo odręczne 8">
@@ -4637,8 +8695,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="12" name="Pismo odręczne 11">
@@ -4657,7 +8715,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="12" name="Pismo odręczne 11">
@@ -4702,8 +8760,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="13" name="Pismo odręczne 12">
@@ -4722,7 +8780,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="13" name="Pismo odręczne 12">
@@ -4767,8 +8825,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>53640</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="14" name="Pismo odręczne 13">
@@ -4787,7 +8845,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="14" name="Pismo odręczne 13">
@@ -4832,8 +8890,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>53640</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="15" name="Pismo odręczne 14">
@@ -4852,7 +8910,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="15" name="Pismo odręczne 14">
@@ -4897,8 +8955,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>53640</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="16" name="Pismo odręczne 15">
@@ -4917,7 +8975,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="16" name="Pismo odręczne 15">
@@ -4962,8 +9020,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>61200</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="17" name="Pismo odręczne 16">
@@ -4982,7 +9040,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="17" name="Pismo odręczne 16">
@@ -5027,8 +9085,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>64080</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="23" name="Pismo odręczne 22">
@@ -5047,7 +9105,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="23" name="Pismo odręczne 22">
@@ -5092,8 +9150,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>38160</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="24" name="Pismo odręczne 23">
@@ -5112,7 +9170,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="24" name="Pismo odręczne 23">
@@ -5157,8 +9215,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>140400</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="27" name="Pismo odręczne 26">
@@ -5177,7 +9235,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="27" name="Pismo odręczne 26">
@@ -5222,8 +9280,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>76320</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="28" name="Pismo odręczne 27">
@@ -5242,7 +9300,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="28" name="Pismo odręczne 27">
@@ -5345,8 +9403,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>99360</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="43" name="Pismo odręczne 42">
@@ -5365,7 +9423,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="43" name="Pismo odręczne 42">
@@ -5410,8 +9468,8 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>107640</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="44" name="Pismo odręczne 43">
@@ -5430,7 +9488,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="44" name="Pismo odręczne 43">
@@ -5475,8 +9533,8 @@
       <xdr:row>39</xdr:row>
       <xdr:rowOff>32040</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="45" name="Pismo odręczne 44">
@@ -5495,7 +9553,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="45" name="Pismo odręczne 44">
@@ -5846,6 +9904,222 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Wykres 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCF5CF0F-8720-43CB-9509-6BFA8ADF7219}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>601680</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>152280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9360</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>164160</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="4" name="Pismo odręczne 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89BA3383-D136-4537-A027-768E0ED3631F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5478480" y="4724280"/>
+            <a:ext cx="17280" cy="11880"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="Pismo odręczne 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89BA3383-D136-4537-A027-768E0ED3631F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5424840" y="4616640"/>
+              <a:ext cx="124920" cy="227520"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>319800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>182520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>320160</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="5" name="Pismo odręczne 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B04D36A3-9D67-44F1-82C8-3E0BB14AFCF1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5196600" y="3474360"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="Pismo odręczne 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B04D36A3-9D67-44F1-82C8-3E0BB14AFCF1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5142600" y="3366720"/>
+              <a:ext cx="108000" cy="216000"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Łącznik prosty 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C08419-B195-4A03-BA4B-3252B92F728D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4808220" y="4206240"/>
+          <a:ext cx="2545080" cy="1760220"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5893,6 +10167,322 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Wykres 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBD8AA70-73A2-4B5B-A374-C4E59747FEC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>357240</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>182520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>403080</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123480</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="4" name="Pismo odręczne 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C494813-061C-4D85-BCFC-9EBD68B63082}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5234040" y="3840120"/>
+            <a:ext cx="1265040" cy="489600"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="Pismo odręczne 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C494813-061C-4D85-BCFC-9EBD68B63082}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5180040" y="3732480"/>
+              <a:ext cx="1372680" cy="705240"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>395400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>136080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>421080</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>122760</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="5" name="Pismo odręczne 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF9EDA38-BE31-443E-AD33-C29B5C9D90A9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5272200" y="3793680"/>
+            <a:ext cx="1244880" cy="352440"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="Pismo odręczne 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF9EDA38-BE31-443E-AD33-C29B5C9D90A9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5218560" y="3686040"/>
+              <a:ext cx="1352520" cy="568080"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>342840</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>350640</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38160</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="14" name="Pismo odręczne 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47ABA66A-1F01-40F8-B160-844A96890F3D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5219640" y="4320360"/>
+            <a:ext cx="617400" cy="106920"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="14" name="Pismo odręczne 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47ABA66A-1F01-40F8-B160-844A96890F3D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5201640" y="4302720"/>
+              <a:ext cx="653040" cy="142560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>143599</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Obraz 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{942941DB-12D5-40B2-B959-8E0DDAA65E4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5928360" cy="3069679"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>80010</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Wykres 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E462113-6B38-4D08-A41D-FF2B849D1D68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -6062,7 +10652,7 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">65 23,'-1'0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1568.13">86 1</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1915.69">86 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1915.68">86 1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2248.87">86 1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2249.87">86 1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2582.03">86 1</inkml:trace>
@@ -6135,6 +10725,93 @@
 </inkml:ink>
 </file>
 
+<file path=xl/ink/ink17.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-23T07:15:27.787"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'3'0,"2"3,4 2,-1 3,3 0,-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink18.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-23T07:15:52.038"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'-1'0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink19.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-23T07:58:03.612"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">24 1,'-1'0,"0"0,0 1,0-1,0 1,0-1,0 1,0-1,0 1,1 0,-1-1,0 1,1 0,-1 0,0-1,1 1,-1 0,1 0,-1 0,1 0,0 0,-1 0,1 0,0 0,-1 0,1 0,0 0,0 1,-4 33,4-31,-3 354,5-183,-4-66,5 120,-2-224,0-1,0 1,0-1,1 0,0 1,0-1,0 0,0 0,1 0,-1-1,1 1,0 0,0-1,1 0,-1 0,0 0,1 0,0 0,0-1,0 0,5 3,10 4,1-1,0-1,25 6,-43-13,21 5,1-1,27 1,22 3,0 1,-52-8,0 1,0 1,33 10,-13 1,83 16,-9-4,-32-6,26-3,33 8,-107-19,0-1,0-1,1-2,44-4,59 4,-98 4,1 2,-2 2,1 2,48 20,-68-26,0 0,0-2,44 4,-6-2,13 2,1-5,75-4,-35-1,713 2,-810-1,0-1,28-6,-27 4,0 1,20-1,-18 3,36-8,-38 5,1 1,26-1,-26 4,-1 0</inkml:trace>
+</inkml:ink>
+</file>
+
 <file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -6161,6 +10838,67 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">1 1,'0'0</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink20.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-23T07:58:14.151"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.3" units="cm"/>
+      <inkml:brushProperty name="height" value="0.6" units="cm"/>
+      <inkml:brushProperty name="color" value="#FFFC00"/>
+      <inkml:brushProperty name="tip" value="rectangle"/>
+      <inkml:brushProperty name="rasterOp" value="maskPen"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">490 130,'8'1,"1"0,0 1,-1 0,1 0,-1 1,16 7,20 7,150 23,-171-36,-14-1,-18-1,-11 2,19 1,14 2,20 3,0 0,1-3,57 7,-49-9,62 16,-90-14,-18-3,-30 1,24-4,-83 10,-190 24,210-22,-131 40,197-51,-33 14,39-16,0 1,0-1,-1 1,1-1,0 1,0 0,0 0,0-1,0 1,0 0,0 0,0 0,1 0,-1 0,0 0,0 0,1 0,-1 0,1 0,-1 0,1 0,-1 1,1-1,-1 3,2-3,0 0,0 0,-1 0,1 1,0-1,0 0,0 0,0 0,0 0,0-1,1 1,-1 0,0 0,0-1,1 1,-1 0,0-1,1 1,-1-1,1 0,1 1,38 10,85 11,-74-14,412 62,377 63,-592-84,-200-32,-48-17,-1 0,1 0,-1 0,1 0,-1 0,0 1,1-1,-1 0,0 0,1 1,-1-1,0 0,1 1,-1-1,0 0,1 1,-1-1,0 0,0 1,0-1,1 0,-1 1,0-1,0 1,0-1,0 1,0-1,0 0,0 1,1-1,-1 1,-1-1,1 1,0-1,0 0,0 1,0-1,0 1,0-1,0 1,-1-1,1 0,0 1,0-1,0 0,-1 1,1-1,0 0,-1 1,1-1,0 0,-1 1,1-1,0 0,-1 0,0 1,-26 12,24-11,-311 112,299-111,1 0,0-1,-22 0,9 0,43 2,22 1,663 5,-463-12,-17 2,-202-1,-19 1,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0-1,0 1,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0-1,0 1,0 0,0 0,0 0,0 0,0 0,0 0,0 0,1 0,-1 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,0 0,1 0,-33-6,-571-44,-3 44,579 4,58-4,485-26,-185 17,-298 11,-28 3,-22-1,-662-14,-117-5,575 13,-585-32,771 38,23 2,1-1,-1 1,0-2,0 0,1 0,-1-1,1-1,-19-7,30 10,-1 1,1 0,0 0,-1 0,1 0,0-1,-1 1,1 0,0 0,0-1,-1 1,1 0,0 0,0-1,-1 1,1 0,0-1,0 1,0 0,-1-1,1 1,0-1,0 1,0 0,0-1,0 1,0 0,0-1,0 1,0-1,0 1,0 0,0-1,0 1,0 0,0-1,1 1,-1-1,0 1,0 0,0-1,1 1,-1 0,0 0,0-1,1 1,-1 0,0-1,0 1,1 0,-1 0,0 0,1-1,0 1,8-5,1 1,0 1,1-1,-1 2,1-1,-1 1,1 1,12-1,-11 1,589-15,-763 56,142-35,-31 5,48-9,-1-1,1 1,-1-1,1 0,0-1,-1 1,1 0,-1-1,1 0,0 0,-5-1,7 1,1 0,-1 1,0-1,1 0,-1 0,0 1,1-1,-1 0,1 0,-1 0,1 0,0 0,-1 0,1 0,0 0,0 0,-1 0,1 0,0 0,0 0,0 0,0 0,0 0,1 0,-1 0,0 1,0-1,1 0,-1 0,0 0,1 0,0-2,20-34,-17 29,5-6,-1 0,-1-1,-1-1,6-19,-10 30,-1 1,0-1,0 1,0-1,-1 1,0-1,0 0,0 1,0-1,-1 1,1-1,-1 0,0 1,-1 0,1-1,-1 1,0 0,0 0,0 0,-4-5,-8-10,1-1,1-1,1 0,-17-45,8 19,8 18,6 13,-1 0,-1 0,-17-26,22 39,-1 0,1 0,0 0,-1 0,0 0,0 1,1 0,-1 0,-1 0,1 0,0 1,0-1,-1 1,-5-1,2 1,1 0,0 0,-1 1,1 0,-1 1,1 0,-15 3,21-4,-2 1,1 0,-1 0,1-1,0 1,-1-1,1 1,-1-1,1 0,-1 0,1 0,-1 0,1-1,-5 0,23-4,89-2,110 7,-93 1,67-2,185 3,-326 1,-1 1,-1 3,1 1,-1 3,-1 1,0 3,-1 1,0 3,60 35,-74-39,-1-2,2 0,-1-2,2-1,47 8,15 6,-43-10,1-2,90 8,-70-11,-37-4,49 0,-63-4,1 1,-1 0,0 2,0 0,24 9,97 43,-117-46,45 25,73 47,-19-10,-49-23,-56-35,0-1,37 19,-48-28,1 0,-1 1,0 0,-1 0,1 1,-1 0,0 1,-1-1,0 1,0 0,6 10,-12-17,0 1,1-1,-1 1,0-1,0 1,1-1,-1 1,0-1,1 1,-1-1,0 1,1-1,-1 1,1-1,-1 0,1 1,-1-1,1 0,-1 0,1 1,-1-1,1 0,0 0,-1 0,1 1,-1-1,1 0,-1 0,1 0,0 0,-1 0,1 0,0 0,0-1,0 0,0 0,0 0,0 0,0 0,0-1,-1 1,1 0,0 0,-1 0,1-1,-1 1,1-2,8-47,-8-167,-3 107,2 95,-2 0,-6-30,4 30,1-1,-1-28,4 16,1 18,-1-1,0 1,0-1,-1 1,-4-17,4 24,0 1,0 0,0-1,0 1,0 0,-1 0,1 0,-1 0,1 0,-1 0,0 0,1 0,-1 1,0-1,0 1,-1-1,1 1,0 0,0 0,-1 0,1 0,0 0,-1 1,1-1,-1 1,1-1,-1 1,-3 0,-174 1,69 2,60-3,-45 0,-111-13,-202-38,288 31,74 11,-88-5,116 12,-1 0,-23-6,-2-1,5 3,2 0,-74-3,-1301 10,2649-1,-1213-1,1-2,22-4,-22 3,40-3,27 7,-42 2,0-3,80-12,-98 9,0 1,55 2,13 0,-35-10,-46 7,0 1,23-1,610 3,-316 3,-318-3,-10 1,0 0,0 0,-1 0,1 1,0 0,10 3,-15-3,0 0,0 0,0 0,-1 0,1 0,0 1,0-1,-1 1,1-1,-1 1,1 0,-1 0,0-1,0 1,0 0,0 0,0 0,0 0,0 1,-1-1,1 0,-1 0,1 0,-1 3,2 16,0-1,-2 1,0-1,-2 1,0-1,-1 0,-1 0,-1 0,-9 24,-77 263,87-289,1-6,2-1,0 1,0 11,-5 33,1-43</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink21.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-03-23T07:58:55.566"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.1" units="cm"/>
+      <inkml:brushProperty name="height" value="0.1" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+      <inkml:brushProperty name="ignorePressure" value="1"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">43 22,'-3'0,"10"0,92 8,57 15,-105-17,177 34,-202-35,1-2,-1-1,42-2,-38-1,-1 1,45 7,109 23,-112-24,-56-6,-1 1,1 1,-1 0,0 0,0 2,0-1,15 8,-22-8,6 4,1-1,0-1,0 0,0-1,21 4,114 13,-63-3,-69-16</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1315.4">1715 297,'-4'0,"-4"0,-5 0,-4 0,2 0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2736.83">22 43,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3359.68">1 1,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3697.27">1 1,'0'0</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4031">1 1,'0'0</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -8343,7 +13081,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7959C761-9782-4DBB-8773-D4E0E0264CBF}">
-  <dimension ref="B3:K15"/>
+  <dimension ref="B3:K49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
@@ -8481,6 +13219,338 @@
         <v>79</v>
       </c>
       <c r="F15" s="2"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>160</v>
+      </c>
+      <c r="E18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>100</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f>D19/C19</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="E20">
+        <f>D19/B19</f>
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f>E24/D24</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+      <c r="E24">
+        <v>200</v>
+      </c>
+      <c r="F24">
+        <f>E24/C24</f>
+        <v>200</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" t="s">
+        <v>163</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f>E28/D28</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>300</v>
+      </c>
+      <c r="F28">
+        <f>E28/C28</f>
+        <v>30</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <f>E33/D33</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>400</v>
+      </c>
+      <c r="F33">
+        <f>E33/C33</f>
+        <v>80</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="1">
+        <v>10</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>124</v>
+      </c>
+      <c r="H39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>10</v>
+      </c>
+      <c r="H40" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C42" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
+        <v>126</v>
+      </c>
+      <c r="H42">
+        <v>100</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>200</v>
+      </c>
+      <c r="H43">
+        <v>200</v>
+      </c>
+      <c r="I43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C45" t="s">
+        <v>168</v>
+      </c>
+      <c r="D45">
+        <f>MDETERM(D42:E43)</f>
+        <v>1900</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="G45" s="16">
+        <f>5*D49+8*D48</f>
+        <v>193.93939393939394</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C46" t="s">
+        <v>169</v>
+      </c>
+      <c r="D46">
+        <f>MDETERM(H42:I43)</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C47" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47">
+        <f>MDETERM(D39:E40)</f>
+        <v>99</v>
+      </c>
+      <c r="F47" t="s">
+        <v>172</v>
+      </c>
+      <c r="G47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I47" t="s">
+        <v>58</v>
+      </c>
+      <c r="J47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D48">
+        <f>D45/D47</f>
+        <v>19.19191919191919</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <f>H49/G49</f>
+        <v>24.2425</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49">
+        <f>D46/D47</f>
+        <v>8.0808080808080813</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>8</v>
+      </c>
+      <c r="H49">
+        <v>193.94</v>
+      </c>
+      <c r="I49">
+        <f>H49/F49</f>
+        <v>38.787999999999997</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8490,7 +13560,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3123175E-9178-423C-891F-842A518B498B}">
-  <dimension ref="B2:N17"/>
+  <dimension ref="B2:Q46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
@@ -8594,7 +13664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>76</v>
       </c>
@@ -8605,6 +13675,770 @@
         <v>91</v>
       </c>
       <c r="E17" s="2"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f>D22/C22</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>30</v>
+      </c>
+      <c r="C22">
+        <v>60</v>
+      </c>
+      <c r="D22">
+        <v>480</v>
+      </c>
+      <c r="E22">
+        <f>D22/B22</f>
+        <v>16</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <f>D26/C26</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>40</v>
+      </c>
+      <c r="C26">
+        <v>15</v>
+      </c>
+      <c r="D26">
+        <v>240</v>
+      </c>
+      <c r="E26">
+        <f>D26/B26</f>
+        <v>6</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <f>D30/C30</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+      <c r="D30">
+        <v>50</v>
+      </c>
+      <c r="E30">
+        <f>D30/B30</f>
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>58</v>
+      </c>
+      <c r="K30" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="I31" t="s">
+        <v>178</v>
+      </c>
+      <c r="J31">
+        <v>6</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <v>6</v>
+      </c>
+      <c r="K32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" t="s">
+        <v>175</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="M33" t="s">
+        <v>40</v>
+      </c>
+      <c r="N33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>177</v>
+      </c>
+      <c r="I34" t="s">
+        <v>180</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="M34" t="s">
+        <v>59</v>
+      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35">
+        <v>30</v>
+      </c>
+      <c r="D35">
+        <v>40</v>
+      </c>
+      <c r="F35" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35">
+        <v>480</v>
+      </c>
+      <c r="J35">
+        <v>20</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+      <c r="M35" t="s">
+        <v>172</v>
+      </c>
+      <c r="N35">
+        <f>5*N33+10*N34</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C36">
+        <v>60</v>
+      </c>
+      <c r="D36">
+        <v>15</v>
+      </c>
+      <c r="G36">
+        <v>240</v>
+      </c>
+      <c r="P36" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="M37">
+        <v>5</v>
+      </c>
+      <c r="N37">
+        <v>10</v>
+      </c>
+      <c r="O37">
+        <v>80</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <f>O37/N37</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38">
+        <v>480</v>
+      </c>
+      <c r="D38">
+        <v>40</v>
+      </c>
+      <c r="F38" t="s">
+        <v>126</v>
+      </c>
+      <c r="G38">
+        <v>30</v>
+      </c>
+      <c r="H38">
+        <v>480</v>
+      </c>
+      <c r="P38">
+        <f>O37/M37</f>
+        <v>16</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="C39">
+        <v>240</v>
+      </c>
+      <c r="D39">
+        <v>15</v>
+      </c>
+      <c r="G39">
+        <v>60</v>
+      </c>
+      <c r="H39">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>168</v>
+      </c>
+      <c r="C41">
+        <f>MDETERM(C38:D39)</f>
+        <v>-2400</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C42">
+        <f>MDETERM(G38:H39)</f>
+        <v>-21600</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>170</v>
+      </c>
+      <c r="C43">
+        <f>MDETERM(C35:D36)</f>
+        <v>-1950</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45">
+        <f>C41/C43</f>
+        <v>1.2307692307692308</v>
+      </c>
+      <c r="E45">
+        <f>5*C45+10*C46</f>
+        <v>116.92307692307693</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46">
+        <f>C42/C43</f>
+        <v>11.076923076923077</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A65E89-03DA-4C76-A708-1EFAF62C49C3}">
+  <dimension ref="A18:L56"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>0.6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>6</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G23" t="s">
+        <v>191</v>
+      </c>
+      <c r="H23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G24" t="s">
+        <v>192</v>
+      </c>
+      <c r="H24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G25" t="s">
+        <v>193</v>
+      </c>
+      <c r="H25" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f>D28/C28</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>20</v>
+      </c>
+      <c r="E28">
+        <f>D28/B28</f>
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>20</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <f>D31/C31</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E32">
+        <f>D31/B31</f>
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <f>D35/C35</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E36">
+        <f>D35/B35</f>
+        <v>6</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>0.6</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <f>D41/C41</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E42">
+        <f>D41/B41</f>
+        <v>10</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>5</v>
+      </c>
+      <c r="E44" t="s">
+        <v>124</v>
+      </c>
+      <c r="F44">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>6</v>
+      </c>
+      <c r="F45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48">
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="F48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+      <c r="H48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C49">
+        <v>12</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51">
+        <f>MDETERM(B44:C45)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52">
+        <f>MDETERM(C48:D49)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53">
+        <f>MDETERM(G48:H49)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="17">
+        <f>C52/C51</f>
+        <v>3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" s="17">
+        <f>C54*0.6+1*C55</f>
+        <v>2.8</v>
+      </c>
+      <c r="K54" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="17">
+        <f>C53/C51</f>
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>199</v>
+      </c>
+      <c r="F55" t="s">
+        <v>200</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <f>J56/I56</f>
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H56">
+        <v>0.6</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>2.8</v>
+      </c>
+      <c r="K56" s="17">
+        <f>J56/H56</f>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/KW1.xlsx
+++ b/KW1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prac608\Desktop\BO_KW1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912B9624-80DF-46C8-AD1D-38DF1D3C548B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5936FE7-041F-4BD0-9A43-7038910947F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{10D9412E-425A-427C-9571-88D404C725CE}"/>
+    <workbookView xWindow="11256" yWindow="0" windowWidth="11460" windowHeight="12540" activeTab="2" xr2:uid="{10D9412E-425A-427C-9571-88D404C725CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Z1" sheetId="1" r:id="rId1"/>
@@ -34,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="240">
   <si>
     <t>Wyrób 1</t>
   </si>
@@ -645,6 +642,123 @@
   </si>
   <si>
     <t>0,6*x1+1*x2=2,80</t>
+  </si>
+  <si>
+    <t>METODA SIMPLEKS</t>
+  </si>
+  <si>
+    <t>Model decyzyjny</t>
+  </si>
+  <si>
+    <t>POSTAĆ KANONICZNA</t>
+  </si>
+  <si>
+    <t>Określenie zmiennych swobodnych</t>
+  </si>
+  <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>X4</t>
+  </si>
+  <si>
+    <t>niewykorzystany zasób 1 środka produkcji</t>
+  </si>
+  <si>
+    <t>niewykorzystany zasób 2 środka produkcji</t>
+  </si>
+  <si>
+    <t>Wprowadzenie zmiennnych swobodnych do FC</t>
+  </si>
+  <si>
+    <t>200*X1+400*X2+0*X3+0*X4 ~~max</t>
+  </si>
+  <si>
+    <t>Wprowadzenie zmiennnych swobodnych do WO-z nierówności tworzymy równania</t>
+  </si>
+  <si>
+    <t>1*X1+4*X2+1*X3=8000</t>
+  </si>
+  <si>
+    <t>3*X1+2*X2+1*X4=9000</t>
+  </si>
+  <si>
+    <t>Wprowadzenie zmiennych swobodnych do WB</t>
+  </si>
+  <si>
+    <t>X1,X2,X3,X4&gt;=0</t>
+  </si>
+  <si>
+    <t>PEŁNY MODEL W POSTACI KANONICZNEJ</t>
+  </si>
+  <si>
+    <t>6. ZAPIS 1 tablicy SIMPLEKS</t>
+  </si>
+  <si>
+    <t>Tablica nr1</t>
+  </si>
+  <si>
+    <t>Cj:</t>
+  </si>
+  <si>
+    <t>wartości</t>
+  </si>
+  <si>
+    <t>Cb:</t>
+  </si>
+  <si>
+    <t>Xb/Xj:</t>
+  </si>
+  <si>
+    <t>1 rozwiązanie bazowe tworzą zmienne swobodne</t>
+  </si>
+  <si>
+    <t>środek tablicy wypełniają parametry z WO</t>
+  </si>
+  <si>
+    <t>bi</t>
+  </si>
+  <si>
+    <t>kolejny wiersz to FC w danym rozwiązniu</t>
+  </si>
+  <si>
+    <t>Zj:</t>
+  </si>
+  <si>
+    <t>wartość FC w danym rozwiąznaiu</t>
+  </si>
+  <si>
+    <t>CJ-ZJ:</t>
+  </si>
+  <si>
+    <t>jeśli w wierszu optymalności występują wartości dodatnie należy skonstruować nowe lepsze nie gorsze rozwiązanie alternatywne</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>x5</t>
+  </si>
+  <si>
+    <t>Cb</t>
+  </si>
+  <si>
+    <t>Xb/Xj</t>
+  </si>
+  <si>
+    <t>Cj-Zj</t>
+  </si>
+  <si>
+    <t>Cj</t>
+  </si>
+  <si>
+    <t>Zj=</t>
+  </si>
+  <si>
+    <t>Cj-zj=</t>
   </si>
 </sst>
 </file>
@@ -719,7 +833,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -742,26 +856,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -775,6 +910,15 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -1440,6 +1584,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1447,7 +1592,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2195,6 +2339,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2202,7 +2347,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2763,6 +2907,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2770,7 +2915,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3305,7 +3449,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="pl-PL"/>
+              <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -3514,6 +3658,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3521,7 +3666,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4336,6 +4480,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4343,7 +4488,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5027,6 +5171,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5034,7 +5179,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9953,8 +10097,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>164160</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Pismo odręczne 3">
@@ -9973,7 +10117,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Pismo odręczne 3">
@@ -10018,8 +10162,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Pismo odręczne 4">
@@ -10038,7 +10182,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Pismo odręczne 4">
@@ -10218,8 +10362,8 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Pismo odręczne 3">
@@ -10238,7 +10382,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Pismo odręczne 3">
@@ -10283,8 +10427,8 @@
       <xdr:row>22</xdr:row>
       <xdr:rowOff>122760</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Pismo odręczne 4">
@@ -10303,7 +10447,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Pismo odręczne 4">
@@ -10348,8 +10492,8 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>38160</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="14" name="Pismo odręczne 13">
@@ -10368,7 +10512,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="14" name="Pismo odręczne 13">
@@ -10652,7 +10796,7 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">65 23,'-1'0</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1568.13">86 1</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1915.68">86 1</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1915.67">86 1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2248.87">86 1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2249.87">86 1</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2582.03">86 1</inkml:trace>
@@ -11390,7 +11534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F75035C-00A0-4345-910D-8DEFF3C6FD49}">
-  <dimension ref="B2:T80"/>
+  <dimension ref="B2:T115"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
@@ -11767,7 +11911,7 @@
       </c>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C31" t="s">
@@ -11780,7 +11924,7 @@
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C45" t="s">
@@ -11802,7 +11946,7 @@
       <c r="D47" t="s">
         <v>114</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="7" t="s">
         <v>115</v>
       </c>
     </row>
@@ -11827,7 +11971,7 @@
       <c r="F50">
         <v>400</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="7">
         <v>800000</v>
       </c>
       <c r="H50" s="5">
@@ -11848,7 +11992,7 @@
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="9" t="s">
         <v>116</v>
       </c>
       <c r="C52" t="s">
@@ -11898,27 +12042,27 @@
       <c r="C60" t="s">
         <v>123</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="10">
         <v>1</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="10">
         <v>4</v>
       </c>
       <c r="G60" t="s">
         <v>124</v>
       </c>
-      <c r="H60" s="12">
+      <c r="H60" s="11">
         <v>8000</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D61" s="11">
+      <c r="D61" s="10">
         <v>3</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="10">
         <v>2</v>
       </c>
-      <c r="H61" s="12">
+      <c r="H61" s="11">
         <v>9000</v>
       </c>
     </row>
@@ -11926,33 +12070,33 @@
       <c r="C63" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="11">
         <v>8000</v>
       </c>
-      <c r="E63" s="11">
+      <c r="E63" s="10">
         <v>4</v>
       </c>
       <c r="G63" t="s">
         <v>126</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="10">
         <v>1</v>
       </c>
-      <c r="I63" s="12">
+      <c r="I63" s="11">
         <v>8000</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="D64" s="12">
+      <c r="D64" s="11">
         <v>9000</v>
       </c>
-      <c r="E64" s="11">
+      <c r="E64" s="10">
         <v>2</v>
       </c>
-      <c r="H64" s="11">
+      <c r="H64" s="10">
         <v>3</v>
       </c>
-      <c r="I64" s="12">
+      <c r="I64" s="11">
         <v>9000</v>
       </c>
     </row>
@@ -11989,14 +12133,14 @@
       </c>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E71" s="14"/>
-      <c r="F71" s="13">
+      <c r="E71" s="13"/>
+      <c r="F71" s="12">
         <f>D68/D67</f>
         <v>2000</v>
       </c>
@@ -12005,14 +12149,14 @@
       </c>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E72" s="14"/>
-      <c r="F72" s="13">
+      <c r="E72" s="13"/>
+      <c r="F72" s="12">
         <f>D69/D67</f>
         <v>1500</v>
       </c>
@@ -12021,7 +12165,7 @@
       </c>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="8" t="s">
         <v>137</v>
       </c>
       <c r="C74" t="s">
@@ -12037,23 +12181,23 @@
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D76" s="15">
+      <c r="D76" s="14">
         <f>200*F71+400*F72</f>
         <v>1000000</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E76" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="8" t="s">
         <v>141</v>
       </c>
       <c r="C77" t="s">
@@ -12098,6 +12242,333 @@
         <v>5000</v>
       </c>
       <c r="G80" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>32</v>
+      </c>
+      <c r="C87" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>36</v>
+      </c>
+      <c r="C88" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>39</v>
+      </c>
+      <c r="C91" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C92" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D92" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C93" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D93" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C95" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B97" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C98" t="s">
+        <v>31</v>
+      </c>
+      <c r="D98" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C99" t="s">
+        <v>32</v>
+      </c>
+      <c r="D99" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C101" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
+        <v>50</v>
+      </c>
+      <c r="C102" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C104" t="s">
+        <v>31</v>
+      </c>
+      <c r="D104" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C105" t="s">
+        <v>32</v>
+      </c>
+      <c r="D105" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C106" t="s">
+        <v>36</v>
+      </c>
+      <c r="D106" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C109" t="s">
+        <v>218</v>
+      </c>
+      <c r="J109" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C110" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D110" s="2">
+        <v>200</v>
+      </c>
+      <c r="E110" s="2">
+        <v>400</v>
+      </c>
+      <c r="F110" s="2">
+        <v>0</v>
+      </c>
+      <c r="G110" s="2">
+        <v>0</v>
+      </c>
+      <c r="H110" t="s">
+        <v>220</v>
+      </c>
+      <c r="J110" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B111" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C111" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D111" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E111" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F111" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="G111" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="H111" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="J111" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B112" s="5">
+        <v>0</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D112" s="5">
+        <v>1</v>
+      </c>
+      <c r="E112" s="5">
+        <v>4</v>
+      </c>
+      <c r="F112" s="5">
+        <v>1</v>
+      </c>
+      <c r="G112" s="5">
+        <v>0</v>
+      </c>
+      <c r="H112" s="5">
+        <v>8000</v>
+      </c>
+      <c r="J112" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B113" s="5">
+        <v>0</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D113" s="5">
+        <v>3</v>
+      </c>
+      <c r="E113" s="5">
+        <v>2</v>
+      </c>
+      <c r="F113" s="5">
+        <v>0</v>
+      </c>
+      <c r="G113" s="5">
+        <v>1</v>
+      </c>
+      <c r="H113" s="5">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C114" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="D114" s="20">
+        <f>SUMPRODUCT($B$112:$B$113,D112:D113)</f>
+        <v>0</v>
+      </c>
+      <c r="E114" s="20">
+        <f t="shared" ref="E114:H114" si="0">SUMPRODUCT($B$112:$B$113,E112:E113)</f>
+        <v>0</v>
+      </c>
+      <c r="F114" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G114" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H114" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I114" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C115" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="D115" s="5">
+        <f>D110-D114</f>
+        <v>200</v>
+      </c>
+      <c r="E115" s="5">
+        <f t="shared" ref="E115:G115" si="1">E110-E114</f>
+        <v>400</v>
+      </c>
+      <c r="F115" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G115" s="5">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -12109,7 +12580,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6773E626-73A8-4CCA-8956-B7CE8B17336F}">
-  <dimension ref="A2:K54"/>
+  <dimension ref="A2:K70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -12189,7 +12660,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B13" t="s">
@@ -12494,7 +12965,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>58</v>
       </c>
@@ -12505,7 +12976,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>59</v>
       </c>
@@ -12513,20 +12984,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C51" s="13" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C51" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13">
+      <c r="E51" s="12"/>
+      <c r="F51" s="12">
         <f>6000</f>
         <v>6000</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F52" t="s">
         <v>40</v>
       </c>
@@ -12534,7 +13005,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C53">
         <v>6000</v>
       </c>
@@ -12552,12 +13023,245 @@
         <v>200</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F54">
         <f>C53/D53</f>
         <v>60</v>
       </c>
       <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>31</v>
+      </c>
+      <c r="B58" t="s">
+        <v>53</v>
+      </c>
+      <c r="E58" t="s">
+        <v>231</v>
+      </c>
+      <c r="F58" t="s">
+        <v>232</v>
+      </c>
+      <c r="G58" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B64" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D64" s="5">
+        <v>100</v>
+      </c>
+      <c r="E64" s="5">
+        <v>30</v>
+      </c>
+      <c r="F64" s="5">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5">
+        <v>0</v>
+      </c>
+      <c r="H64" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B65" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I65" s="17" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B66" s="5">
+        <v>0</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D66" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="E66" s="5">
+        <v>2E-3</v>
+      </c>
+      <c r="F66" s="5">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5">
+        <v>0</v>
+      </c>
+      <c r="H66" s="5">
+        <v>0</v>
+      </c>
+      <c r="I66" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B67" s="5">
+        <v>0</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="E67" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F67" s="5">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5">
+        <v>1</v>
+      </c>
+      <c r="H67" s="5">
+        <v>0</v>
+      </c>
+      <c r="I67" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B68" s="5">
+        <v>0</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D68" s="5">
+        <v>3</v>
+      </c>
+      <c r="E68" s="5">
+        <v>2</v>
+      </c>
+      <c r="F68" s="5">
+        <v>0</v>
+      </c>
+      <c r="G68" s="5">
+        <v>0</v>
+      </c>
+      <c r="H68" s="5">
+        <v>1</v>
+      </c>
+      <c r="I68" s="20">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C69" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D69" s="5">
+        <f>SUMPRODUCT(B66:B68,D66:D68)</f>
+        <v>0</v>
+      </c>
+      <c r="E69" s="5">
+        <f>SUMPRODUCT(B66:B68,E66:E68)</f>
+        <v>0</v>
+      </c>
+      <c r="F69" s="5">
+        <f>SUMPRODUCT(B66:B68,F66:F68)</f>
+        <v>0</v>
+      </c>
+      <c r="G69" s="5">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5">
+        <f>SUMPRODUCT(B66:B68,I66:I68)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C70" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D70" s="5">
+        <f>D64-D69</f>
+        <v>100</v>
+      </c>
+      <c r="E70" s="5">
+        <f t="shared" ref="E70:H70" si="0">E64-E69</f>
+        <v>30</v>
+      </c>
+      <c r="F70" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G70" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="5">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -12569,7 +13273,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1389125F-4D16-4B83-9402-0C5CDA76E2BD}">
-  <dimension ref="A2:L63"/>
+  <dimension ref="A2:L80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.5546875" customWidth="1"/>
@@ -13071,6 +13775,218 @@
       <c r="C63" t="e">
         <f>MDETERM(C55:D57)</f>
         <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>32</v>
+      </c>
+      <c r="B69" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>68</v>
+      </c>
+      <c r="B71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>17</v>
+      </c>
+      <c r="B72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>237</v>
+      </c>
+      <c r="C74">
+        <v>20</v>
+      </c>
+      <c r="D74">
+        <v>30</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>234</v>
+      </c>
+      <c r="B75" t="s">
+        <v>235</v>
+      </c>
+      <c r="C75" t="s">
+        <v>58</v>
+      </c>
+      <c r="D75" t="s">
+        <v>59</v>
+      </c>
+      <c r="E75" t="s">
+        <v>231</v>
+      </c>
+      <c r="F75" t="s">
+        <v>232</v>
+      </c>
+      <c r="G75" t="s">
+        <v>233</v>
+      </c>
+      <c r="H75" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>0</v>
+      </c>
+      <c r="B76" t="s">
+        <v>231</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>0.5</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>0</v>
+      </c>
+      <c r="B77" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77">
+        <v>0.5</v>
+      </c>
+      <c r="D77">
+        <v>0.6</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>0</v>
+      </c>
+      <c r="B78" t="s">
+        <v>233</v>
+      </c>
+      <c r="C78">
+        <v>0.2</v>
+      </c>
+      <c r="D78">
+        <v>0.3</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>238</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>239</v>
+      </c>
+      <c r="C80">
+        <f>C74-C79</f>
+        <v>20</v>
+      </c>
+      <c r="D80">
+        <f t="shared" ref="D80:G80" si="0">D74-D79</f>
+        <v>30</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13473,10 +14389,10 @@
         <f>MDETERM(D42:E43)</f>
         <v>1900</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="15">
         <f>5*D49+8*D48</f>
         <v>193.93939393939394</v>
       </c>
@@ -14382,14 +15298,14 @@
       <c r="B54" t="s">
         <v>40</v>
       </c>
-      <c r="C54" s="17">
+      <c r="C54" s="16">
         <f>C52/C51</f>
         <v>3</v>
       </c>
       <c r="E54" t="s">
         <v>198</v>
       </c>
-      <c r="F54" s="17">
+      <c r="F54" s="16">
         <f>C54*0.6+1*C55</f>
         <v>2.8</v>
       </c>
@@ -14404,7 +15320,7 @@
       <c r="B55" t="s">
         <v>119</v>
       </c>
-      <c r="C55" s="17">
+      <c r="C55" s="16">
         <f>C53/C51</f>
         <v>1</v>
       </c>
@@ -14432,7 +15348,7 @@
       <c r="J56">
         <v>2.8</v>
       </c>
-      <c r="K56" s="17">
+      <c r="K56" s="16">
         <f>J56/H56</f>
         <v>4.666666666666667</v>
       </c>
